--- a/dist/finengine.xlsx
+++ b/dist/finengine.xlsx
@@ -18,6 +18,12 @@
     <sheet name="HoldCo_IS" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="HoldCo_BS" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="HoldCo_CF" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="IC_Register" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IC_Recon" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Eliminations" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Consol_IS" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Consol_BS" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Consol_CF" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,7 +82,7 @@
       <color rgb="00007000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +104,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +156,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3276,6 +3289,2979 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>内部交易登记簿</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>四类关联交易 · 金额公式全链接单体表 | 万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>科目（万元）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>── 当年交易额 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    T1 license · 研究院 → 智擎云</t>
+        </is>
+      </c>
+      <c r="C5" s="20">
+        <f>Cloud_IS!C4*Assumptions!C48</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>Cloud_IS!D4*Assumptions!D48</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>Cloud_IS!E4*Assumptions!E48</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>Cloud_IS!F4*Assumptions!F48</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>Cloud_IS!G4*Assumptions!G48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    T1 license · 研究院 → 智擎行业</t>
+        </is>
+      </c>
+      <c r="C6" s="20">
+        <f>Ind_IS!C6*Assumptions!C49</f>
+        <v/>
+      </c>
+      <c r="D6" s="20">
+        <f>Ind_IS!D6*Assumptions!D49</f>
+        <v/>
+      </c>
+      <c r="E6" s="20">
+        <f>Ind_IS!E6*Assumptions!E49</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>Ind_IS!F6*Assumptions!F49</f>
+        <v/>
+      </c>
+      <c r="G6" s="20">
+        <f>Ind_IS!G6*Assumptions!G49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    T1 license · 研究院 → 智擎互联</t>
+        </is>
+      </c>
+      <c r="C7" s="20">
+        <f>Toc_IS!C6*Assumptions!C50</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>Toc_IS!D6*Assumptions!D50</f>
+        <v/>
+      </c>
+      <c r="E7" s="20">
+        <f>Toc_IS!E6*Assumptions!E50</f>
+        <v/>
+      </c>
+      <c r="F7" s="20">
+        <f>Toc_IS!F6*Assumptions!F50</f>
+        <v/>
+      </c>
+      <c r="G7" s="20">
+        <f>Toc_IS!G6*Assumptions!G50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    T2 定制研发 · 研究院 → 智擎行业</t>
+        </is>
+      </c>
+      <c r="C8" s="20">
+        <f>Assumptions!C51</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>Assumptions!D51</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>Assumptions!E51</f>
+        <v/>
+      </c>
+      <c r="F8" s="20">
+        <f>Assumptions!F51</f>
+        <v/>
+      </c>
+      <c r="G8" s="20">
+        <f>Assumptions!G51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    T3 算力服务 · 智擎云 → 智擎互联</t>
+        </is>
+      </c>
+      <c r="C9" s="20">
+        <f>Assumptions!C31*Assumptions!C35*12*Assumptions!C52</f>
+        <v/>
+      </c>
+      <c r="D9" s="20">
+        <f>Assumptions!D31*Assumptions!D35*12*Assumptions!D52</f>
+        <v/>
+      </c>
+      <c r="E9" s="20">
+        <f>Assumptions!E31*Assumptions!E35*12*Assumptions!E52</f>
+        <v/>
+      </c>
+      <c r="F9" s="20">
+        <f>Assumptions!F31*Assumptions!F35*12*Assumptions!F52</f>
+        <v/>
+      </c>
+      <c r="G9" s="20">
+        <f>Assumptions!G31*Assumptions!G35*12*Assumptions!G52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    关联交易合计</t>
+        </is>
+      </c>
+      <c r="C10" s="17">
+        <f>SUM(IC_Register!C5,IC_Register!C6,IC_Register!C7,IC_Register!C8,IC_Register!C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>SUM(IC_Register!D5,IC_Register!D6,IC_Register!D7,IC_Register!D8,IC_Register!D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>SUM(IC_Register!E5,IC_Register!E6,IC_Register!E7,IC_Register!E8,IC_Register!E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>SUM(IC_Register!F5,IC_Register!F6,IC_Register!F7,IC_Register!F8,IC_Register!F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>SUM(IC_Register!G5,IC_Register!G6,IC_Register!G7,IC_Register!G8,IC_Register!G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>── 期末往来余额（账期60天挂账）──</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    研究院 应收三家（借方）</t>
+        </is>
+      </c>
+      <c r="C12" s="20">
+        <f>(IC_Register!C5+IC_Register!C6+IC_Register!C7+IC_Register!C8)*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f>(IC_Register!D5+IC_Register!D6+IC_Register!D7+IC_Register!D8)*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
+        <f>(IC_Register!E5+IC_Register!E6+IC_Register!E7+IC_Register!E8)*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f>(IC_Register!F5+IC_Register!F6+IC_Register!F7+IC_Register!F8)*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G12" s="20">
+        <f>(IC_Register!G5+IC_Register!G6+IC_Register!G7+IC_Register!G8)*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    智擎云 应收互联（T3）</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2027 未含未开票 220</t>
+        </is>
+      </c>
+      <c r="C13" s="20">
+        <f>IC_Register!C9*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
+        <f>IC_Register!D9*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E13" s="20">
+        <f>IC_Register!E9*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F13" s="20">
+        <f>IC_Register!F9*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G13" s="20">
+        <f>IC_Register!G9*Assumptions!G8/365-Assumptions!G54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    智擎云 应付研究院（T1）</t>
+        </is>
+      </c>
+      <c r="C14" s="20">
+        <f>IC_Register!C5*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D14" s="20">
+        <f>IC_Register!D5*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E14" s="20">
+        <f>IC_Register!E5*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F14" s="20">
+        <f>IC_Register!F5*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G14" s="20">
+        <f>IC_Register!G5*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    智擎行业 应付研究院（T1+T2）</t>
+        </is>
+      </c>
+      <c r="C15" s="20">
+        <f>(IC_Register!C6+IC_Register!C8)*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
+        <f>(IC_Register!D6+IC_Register!D8)*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E15" s="20">
+        <f>(IC_Register!E6+IC_Register!E8)*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F15" s="20">
+        <f>(IC_Register!F6+IC_Register!F8)*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G15" s="20">
+        <f>(IC_Register!G6+IC_Register!G8)*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    智擎互联 应付（T3+T1，含在途）</t>
+        </is>
+      </c>
+      <c r="C16" s="20">
+        <f>(IC_Register!C9+IC_Register!C7)*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D16" s="20">
+        <f>(IC_Register!D9+IC_Register!D7)*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E16" s="20">
+        <f>(IC_Register!E9+IC_Register!E7)*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F16" s="20">
+        <f>(IC_Register!F9+IC_Register!F7)*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G16" s="20">
+        <f>(IC_Register!G9+IC_Register!G7)*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    内部应收合计</t>
+        </is>
+      </c>
+      <c r="C17" s="17">
+        <f>IC_Register!C12+IC_Register!C13</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>IC_Register!D12+IC_Register!D13</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>IC_Register!E12+IC_Register!E13</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>IC_Register!F12+IC_Register!F13</f>
+        <v/>
+      </c>
+      <c r="G17" s="17">
+        <f>IC_Register!G12+IC_Register!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    内部应付合计</t>
+        </is>
+      </c>
+      <c r="C18" s="17">
+        <f>IC_Register!C14+IC_Register!C15+IC_Register!C16</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>IC_Register!D14+IC_Register!D15+IC_Register!D16</f>
+        <v/>
+      </c>
+      <c r="E18" s="17">
+        <f>IC_Register!E14+IC_Register!E15+IC_Register!E16</f>
+        <v/>
+      </c>
+      <c r="F18" s="17">
+        <f>IC_Register!F14+IC_Register!F15+IC_Register!F16</f>
+        <v/>
+      </c>
+      <c r="G18" s="17">
+        <f>IC_Register!G14+IC_Register!G15+IC_Register!G16</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>关联方对账矩阵 · 双边核对 + 在途调节</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>差异可见 → 调节 → 归零 | 万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>科目（万元）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>── 双边核对（A 账上应收 B  vs  B 账上应付 A）──</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    研究院 ↔ 智擎云：研究院应收</t>
+        </is>
+      </c>
+      <c r="C5" s="20">
+        <f>IC_Register!C5*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>IC_Register!D5*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>IC_Register!E5*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>IC_Register!F5*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>IC_Register!G5*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    研究院 ↔ 智擎云：云应付</t>
+        </is>
+      </c>
+      <c r="C6" s="20">
+        <f>IC_Register!C14</f>
+        <v/>
+      </c>
+      <c r="D6" s="20">
+        <f>IC_Register!D14</f>
+        <v/>
+      </c>
+      <c r="E6" s="20">
+        <f>IC_Register!E14</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>IC_Register!F14</f>
+        <v/>
+      </c>
+      <c r="G6" s="20">
+        <f>IC_Register!G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    差异</t>
+        </is>
+      </c>
+      <c r="C7" s="17">
+        <f>IC_Recon!C5-IC_Recon!C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>IC_Recon!D5-IC_Recon!D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>IC_Recon!E5-IC_Recon!E6</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>IC_Recon!F5-IC_Recon!F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>IC_Recon!G5-IC_Recon!G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    研究院 ↔ 智擎行业：研究院应收</t>
+        </is>
+      </c>
+      <c r="C9" s="20">
+        <f>(IC_Register!C6+IC_Register!C8)*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D9" s="20">
+        <f>(IC_Register!D6+IC_Register!D8)*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E9" s="20">
+        <f>(IC_Register!E6+IC_Register!E8)*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F9" s="20">
+        <f>(IC_Register!F6+IC_Register!F8)*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G9" s="20">
+        <f>(IC_Register!G6+IC_Register!G8)*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    研究院 ↔ 智擎行业：行业应付</t>
+        </is>
+      </c>
+      <c r="C10" s="20">
+        <f>IC_Register!C15</f>
+        <v/>
+      </c>
+      <c r="D10" s="20">
+        <f>IC_Register!D15</f>
+        <v/>
+      </c>
+      <c r="E10" s="20">
+        <f>IC_Register!E15</f>
+        <v/>
+      </c>
+      <c r="F10" s="20">
+        <f>IC_Register!F15</f>
+        <v/>
+      </c>
+      <c r="G10" s="20">
+        <f>IC_Register!G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    差异</t>
+        </is>
+      </c>
+      <c r="C11" s="17">
+        <f>IC_Recon!C9-IC_Recon!C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>IC_Recon!D9-IC_Recon!D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>IC_Recon!E9-IC_Recon!E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>IC_Recon!F9-IC_Recon!F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>IC_Recon!G9-IC_Recon!G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    研究院 ↔ 智擎互联：研究院应收</t>
+        </is>
+      </c>
+      <c r="C13" s="20">
+        <f>IC_Register!C7*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
+        <f>IC_Register!D7*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E13" s="20">
+        <f>IC_Register!E7*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F13" s="20">
+        <f>IC_Register!F7*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G13" s="20">
+        <f>IC_Register!G7*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    研究院 ↔ 智擎互联：互联应付（T1部分）</t>
+        </is>
+      </c>
+      <c r="C14" s="20">
+        <f>IC_Register!C7*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D14" s="20">
+        <f>IC_Register!D7*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E14" s="20">
+        <f>IC_Register!E7*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F14" s="20">
+        <f>IC_Register!F7*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G14" s="20">
+        <f>IC_Register!G7*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    差异</t>
+        </is>
+      </c>
+      <c r="C15" s="17">
+        <f>IC_Recon!C13-IC_Recon!C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>IC_Recon!D13-IC_Recon!D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>IC_Recon!E13-IC_Recon!E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>IC_Recon!F13-IC_Recon!F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>IC_Recon!G13-IC_Recon!G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    智擎云 ↔ 智擎互联：云应收（未开票−220）</t>
+        </is>
+      </c>
+      <c r="C17" s="20">
+        <f>IC_Register!C13</f>
+        <v/>
+      </c>
+      <c r="D17" s="20">
+        <f>IC_Register!D13</f>
+        <v/>
+      </c>
+      <c r="E17" s="20">
+        <f>IC_Register!E13</f>
+        <v/>
+      </c>
+      <c r="F17" s="20">
+        <f>IC_Register!F13</f>
+        <v/>
+      </c>
+      <c r="G17" s="20">
+        <f>IC_Register!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    智擎云 ↔ 智擎互联：互联应付（全额挂账）</t>
+        </is>
+      </c>
+      <c r="C18" s="20">
+        <f>IC_Register!C9*Assumptions!C8/365</f>
+        <v/>
+      </c>
+      <c r="D18" s="20">
+        <f>IC_Register!D9*Assumptions!D8/365</f>
+        <v/>
+      </c>
+      <c r="E18" s="20">
+        <f>IC_Register!E9*Assumptions!E8/365</f>
+        <v/>
+      </c>
+      <c r="F18" s="20">
+        <f>IC_Register!F9*Assumptions!F8/365</f>
+        <v/>
+      </c>
+      <c r="G18" s="20">
+        <f>IC_Register!G9*Assumptions!G8/365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    差异（2027 = 在途 220）</t>
+        </is>
+      </c>
+      <c r="C19" s="25">
+        <f>IC_Recon!C17-IC_Recon!C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="25">
+        <f>IC_Recon!D17-IC_Recon!D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="25">
+        <f>IC_Recon!E17-IC_Recon!E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="25">
+        <f>IC_Recon!F17-IC_Recon!F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="25">
+        <f>IC_Recon!G17-IC_Recon!G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>── 在途调节表（cut-off：互联12月已确认，云次年1月开票）──</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    调节前差异</t>
+        </is>
+      </c>
+      <c r="C21" s="20">
+        <f>IC_Recon!C19</f>
+        <v/>
+      </c>
+      <c r="D21" s="20">
+        <f>IC_Recon!D19</f>
+        <v/>
+      </c>
+      <c r="E21" s="20">
+        <f>IC_Recon!E19</f>
+        <v/>
+      </c>
+      <c r="F21" s="20">
+        <f>IC_Recon!F19</f>
+        <v/>
+      </c>
+      <c r="G21" s="20">
+        <f>IC_Recon!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    加：云未开票在途服务</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>服务已提供、发票在途</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="20">
+        <f>Assumptions!G54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    调节后差异（应全 0）</t>
+        </is>
+      </c>
+      <c r="C23" s="22">
+        <f>IC_Recon!C21+IC_Recon!C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="22">
+        <f>IC_Recon!D21+IC_Recon!D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="22">
+        <f>IC_Recon!E21+IC_Recon!E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="22">
+        <f>IC_Recon!F21+IC_Recon!F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="22">
+        <f>IC_Recon!G21+IC_Recon!G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    合并抵消口径（双边孰低=调节后应收方）</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Eliminations E2 引用此行</t>
+        </is>
+      </c>
+      <c r="C25" s="17">
+        <f>IC_Recon!C17+IC_Recon!C22</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>IC_Recon!D17+IC_Recon!D22</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>IC_Recon!E17+IC_Recon!E22</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>IC_Recon!F17+IC_Recon!F22</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>IC_Recon!G17+IC_Recon!G22</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B050"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>合并抵消分录底稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>E0 长投×权益 · E1 关联交易 · E2 内部往来 · E3 少数股东 | 万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>科目（万元）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>── E0 长期股权投资 × 子公司权益（母公司份额）──</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    借：实收资本 · 智擎云</t>
+        </is>
+      </c>
+      <c r="C5" s="20">
+        <f>Cloud_BS_CF!C13</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>Cloud_BS_CF!D13</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>Cloud_BS_CF!E13</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>Cloud_BS_CF!F13</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>Cloud_BS_CF!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    借：未分配利润 · 智擎云</t>
+        </is>
+      </c>
+      <c r="C6" s="20">
+        <f>Cloud_BS_CF!C14</f>
+        <v/>
+      </c>
+      <c r="D6" s="20">
+        <f>Cloud_BS_CF!D14</f>
+        <v/>
+      </c>
+      <c r="E6" s="20">
+        <f>Cloud_BS_CF!E14</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>Cloud_BS_CF!F14</f>
+        <v/>
+      </c>
+      <c r="G6" s="20">
+        <f>Cloud_BS_CF!G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    贷：长投 · 智擎云（成本法）</t>
+        </is>
+      </c>
+      <c r="C7" s="20">
+        <f>10000+SUM(Assumptions!$C57:C57)</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>10000+SUM(Assumptions!$C57:D57)</f>
+        <v/>
+      </c>
+      <c r="E7" s="20">
+        <f>10000+SUM(Assumptions!$C57:E57)</f>
+        <v/>
+      </c>
+      <c r="F7" s="20">
+        <f>10000+SUM(Assumptions!$C57:F57)</f>
+        <v/>
+      </c>
+      <c r="G7" s="20">
+        <f>10000+SUM(Assumptions!$C57:G57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    借：实收资本 · 智擎行业</t>
+        </is>
+      </c>
+      <c r="C8" s="20">
+        <f>Ind_BS_CF!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>Ind_BS_CF!D10</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>Ind_BS_CF!E10</f>
+        <v/>
+      </c>
+      <c r="F8" s="20">
+        <f>Ind_BS_CF!F10</f>
+        <v/>
+      </c>
+      <c r="G8" s="20">
+        <f>Ind_BS_CF!G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    借：未分配利润 · 智擎行业</t>
+        </is>
+      </c>
+      <c r="C9" s="20">
+        <f>Ind_BS_CF!C11</f>
+        <v/>
+      </c>
+      <c r="D9" s="20">
+        <f>Ind_BS_CF!D11</f>
+        <v/>
+      </c>
+      <c r="E9" s="20">
+        <f>Ind_BS_CF!E11</f>
+        <v/>
+      </c>
+      <c r="F9" s="20">
+        <f>Ind_BS_CF!F11</f>
+        <v/>
+      </c>
+      <c r="G9" s="20">
+        <f>Ind_BS_CF!G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    贷：长投 · 智擎行业（成本法）</t>
+        </is>
+      </c>
+      <c r="C10" s="20">
+        <f>8000+SUM(Assumptions!$C58:C58)</f>
+        <v/>
+      </c>
+      <c r="D10" s="20">
+        <f>8000+SUM(Assumptions!$C58:D58)</f>
+        <v/>
+      </c>
+      <c r="E10" s="20">
+        <f>8000+SUM(Assumptions!$C58:E58)</f>
+        <v/>
+      </c>
+      <c r="F10" s="20">
+        <f>8000+SUM(Assumptions!$C58:F58)</f>
+        <v/>
+      </c>
+      <c r="G10" s="20">
+        <f>8000+SUM(Assumptions!$C58:G58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    借：实收资本 · 智擎互联</t>
+        </is>
+      </c>
+      <c r="C11" s="20">
+        <f>Toc_BS_CF!C10*0.8</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
+        <f>Toc_BS_CF!D10*0.8</f>
+        <v/>
+      </c>
+      <c r="E11" s="20">
+        <f>Toc_BS_CF!E10*0.8</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>Toc_BS_CF!F10*0.8</f>
+        <v/>
+      </c>
+      <c r="G11" s="20">
+        <f>Toc_BS_CF!G10*0.8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    借：未分配利润 · 智擎互联</t>
+        </is>
+      </c>
+      <c r="C12" s="20">
+        <f>Toc_BS_CF!C11*0.8</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f>Toc_BS_CF!D11*0.8</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
+        <f>Toc_BS_CF!E11*0.8</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f>Toc_BS_CF!F11*0.8</f>
+        <v/>
+      </c>
+      <c r="G12" s="20">
+        <f>Toc_BS_CF!G11*0.8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    贷：长投 · 智擎互联（成本法）</t>
+        </is>
+      </c>
+      <c r="C13" s="20">
+        <f>5000+SUM(Assumptions!$C59:C59)*0.8</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
+        <f>5000+SUM(Assumptions!$C59:D59)*0.8</f>
+        <v/>
+      </c>
+      <c r="E13" s="20">
+        <f>5000+SUM(Assumptions!$C59:E59)*0.8</f>
+        <v/>
+      </c>
+      <c r="F13" s="20">
+        <f>5000+SUM(Assumptions!$C59:F59)*0.8</f>
+        <v/>
+      </c>
+      <c r="G13" s="20">
+        <f>5000+SUM(Assumptions!$C59:G59)*0.8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    E0 差额 → 合并资本公积（Σ借−Σ贷）</t>
+        </is>
+      </c>
+      <c r="C14" s="17">
+        <f>Eliminations!C5+Eliminations!C6-Eliminations!C7+Eliminations!C8+Eliminations!C9-Eliminations!C10+Eliminations!C11+Eliminations!C12-Eliminations!C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>Eliminations!D5+Eliminations!D6-Eliminations!D7+Eliminations!D8+Eliminations!D9-Eliminations!D10+Eliminations!D11+Eliminations!D12-Eliminations!D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>Eliminations!E5+Eliminations!E6-Eliminations!E7+Eliminations!E8+Eliminations!E9-Eliminations!E10+Eliminations!E11+Eliminations!E12-Eliminations!E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>Eliminations!F5+Eliminations!F6-Eliminations!F7+Eliminations!F8+Eliminations!F9-Eliminations!F10+Eliminations!F11+Eliminations!F12-Eliminations!F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>Eliminations!G5+Eliminations!G6-Eliminations!G7+Eliminations!G8+Eliminations!G9-Eliminations!G10+Eliminations!G11+Eliminations!G12-Eliminations!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>── E1 关联收入 × 关联成本对冲 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    借：关联收入 / 贷：关联成本（全额）</t>
+        </is>
+      </c>
+      <c r="C16" s="17">
+        <f>IC_Register!C10</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>IC_Register!D10</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>IC_Register!E10</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>IC_Register!F10</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>IC_Register!G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>── E2 内部往来对冲（双边孰低=调节后）──</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    借：内部应付合计</t>
+        </is>
+      </c>
+      <c r="C18" s="20">
+        <f>IC_Register!C18</f>
+        <v/>
+      </c>
+      <c r="D18" s="20">
+        <f>IC_Register!D18</f>
+        <v/>
+      </c>
+      <c r="E18" s="20">
+        <f>IC_Register!E18</f>
+        <v/>
+      </c>
+      <c r="F18" s="20">
+        <f>IC_Register!F18</f>
+        <v/>
+      </c>
+      <c r="G18" s="20">
+        <f>IC_Register!G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    贷：内部应收合计（孰低=ΣAR）</t>
+        </is>
+      </c>
+      <c r="C19" s="20">
+        <f>IC_Register!C17</f>
+        <v/>
+      </c>
+      <c r="D19" s="20">
+        <f>IC_Register!D17</f>
+        <v/>
+      </c>
+      <c r="E19" s="20">
+        <f>IC_Register!E17</f>
+        <v/>
+      </c>
+      <c r="F19" s="20">
+        <f>IC_Register!F17</f>
+        <v/>
+      </c>
+      <c r="G19" s="20">
+        <f>IC_Register!G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    差额 → 其他应付款·内部在途（=ΣAP−ΣAR）</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>cut-off 在途挂账</t>
+        </is>
+      </c>
+      <c r="C20" s="17">
+        <f>Eliminations!C18-Eliminations!C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>Eliminations!D18-Eliminations!D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
+        <f>Eliminations!E18-Eliminations!E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="17">
+        <f>Eliminations!F18-Eliminations!F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="17">
+        <f>Eliminations!G18-Eliminations!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>── E3 少数股东（利润拆分，非借贷）──</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    少数股东损益 = 互联 NI × 20%</t>
+        </is>
+      </c>
+      <c r="C22" s="20">
+        <f>Toc_IS!C17*0.2</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>Toc_IS!D17*0.2</f>
+        <v/>
+      </c>
+      <c r="E22" s="20">
+        <f>Toc_IS!E17*0.2</f>
+        <v/>
+      </c>
+      <c r="F22" s="20">
+        <f>Toc_IS!F17*0.2</f>
+        <v/>
+      </c>
+      <c r="G22" s="20">
+        <f>Toc_IS!G17*0.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    少数股东权益 = 互联净资产 × 20%</t>
+        </is>
+      </c>
+      <c r="C23" s="20">
+        <f>(Toc_BS_CF!C10+Toc_BS_CF!C11)*0.2</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
+        <f>(Toc_BS_CF!D10+Toc_BS_CF!D11)*0.2</f>
+        <v/>
+      </c>
+      <c r="E23" s="20">
+        <f>(Toc_BS_CF!E10+Toc_BS_CF!E11)*0.2</f>
+        <v/>
+      </c>
+      <c r="F23" s="20">
+        <f>(Toc_BS_CF!F10+Toc_BS_CF!F11)*0.2</f>
+        <v/>
+      </c>
+      <c r="G23" s="20">
+        <f>(Toc_BS_CF!G10+Toc_BS_CF!G11)*0.2</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B050"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>智擎集团 · 合并利润表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Σ四主体 − E1 关联对冲 − E3 归属拆分 | 万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>科目（万元）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    对外收入合计（云+行业+互联）</t>
+        </is>
+      </c>
+      <c r="C4" s="17">
+        <f>Cloud_IS!C4+Ind_IS!C6+Toc_IS!C6</f>
+        <v/>
+      </c>
+      <c r="D4" s="17">
+        <f>Cloud_IS!D4+Ind_IS!D6+Toc_IS!D6</f>
+        <v/>
+      </c>
+      <c r="E4" s="17">
+        <f>Cloud_IS!E4+Ind_IS!E6+Toc_IS!E6</f>
+        <v/>
+      </c>
+      <c r="F4" s="17">
+        <f>Cloud_IS!F4+Ind_IS!F6+Toc_IS!F6</f>
+        <v/>
+      </c>
+      <c r="G4" s="17">
+        <f>Cloud_IS!G4+Ind_IS!G6+Toc_IS!G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    减：关联收入抵消（E1）</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>T1+T2+T3 全消</t>
+        </is>
+      </c>
+      <c r="C5" s="20">
+        <f>-Eliminations!C16</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>-Eliminations!D16</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>-Eliminations!E16</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>-Eliminations!F16</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>-Eliminations!G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    合并营业收入</t>
+        </is>
+      </c>
+      <c r="C6" s="17">
+        <f>Consol_IS!C4</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>Consol_IS!D4</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>Consol_IS!E4</f>
+        <v/>
+      </c>
+      <c r="F6" s="17">
+        <f>Consol_IS!F4</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>Consol_IS!G4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Σ四主体营业成本</t>
+        </is>
+      </c>
+      <c r="C7" s="20">
+        <f>HoldCo_IS!C7+Cloud_IS!C11+Ind_IS!C11+Toc_IS!C9</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>HoldCo_IS!D7+Cloud_IS!D11+Ind_IS!D11+Toc_IS!D9</f>
+        <v/>
+      </c>
+      <c r="E7" s="20">
+        <f>HoldCo_IS!E7+Cloud_IS!E11+Ind_IS!E11+Toc_IS!E9</f>
+        <v/>
+      </c>
+      <c r="F7" s="20">
+        <f>HoldCo_IS!F7+Cloud_IS!F11+Ind_IS!F11+Toc_IS!F9</f>
+        <v/>
+      </c>
+      <c r="G7" s="20">
+        <f>HoldCo_IS!G7+Cloud_IS!G11+Ind_IS!G11+Toc_IS!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    减：关联成本对冲（E1）</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>含保留云真实服务成本，净效应=−0.45×T3</t>
+        </is>
+      </c>
+      <c r="C8" s="20">
+        <f>-Eliminations!C16</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>-Eliminations!D16</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>-Eliminations!E16</f>
+        <v/>
+      </c>
+      <c r="F8" s="20">
+        <f>-Eliminations!F16</f>
+        <v/>
+      </c>
+      <c r="G8" s="20">
+        <f>-Eliminations!G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    合并营业成本</t>
+        </is>
+      </c>
+      <c r="C9" s="17">
+        <f>Consol_IS!C7+Consol_IS!C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
+        <f>Consol_IS!D7+Consol_IS!D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>Consol_IS!E7+Consol_IS!E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="17">
+        <f>Consol_IS!F7+Consol_IS!F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="17">
+        <f>Consol_IS!G7+Consol_IS!G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    合并毛利润</t>
+        </is>
+      </c>
+      <c r="C10" s="17">
+        <f>Consol_IS!C6-Consol_IS!C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>Consol_IS!D6-Consol_IS!D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>Consol_IS!E6-Consol_IS!E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>Consol_IS!F6-Consol_IS!F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>Consol_IS!G6-Consol_IS!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    研发费用</t>
+        </is>
+      </c>
+      <c r="C11" s="20">
+        <f>Cloud_IS!C13+Ind_IS!C13+Toc_IS!C11+HoldCo_IS!C9</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
+        <f>Cloud_IS!D13+Ind_IS!D13+Toc_IS!D11+HoldCo_IS!D9</f>
+        <v/>
+      </c>
+      <c r="E11" s="20">
+        <f>Cloud_IS!E13+Ind_IS!E13+Toc_IS!E11+HoldCo_IS!E9</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>Cloud_IS!F13+Ind_IS!F13+Toc_IS!F11+HoldCo_IS!F9</f>
+        <v/>
+      </c>
+      <c r="G11" s="20">
+        <f>Cloud_IS!G13+Ind_IS!G13+Toc_IS!G11+HoldCo_IS!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    销售费用</t>
+        </is>
+      </c>
+      <c r="C12" s="20">
+        <f>Cloud_IS!C14+Ind_IS!C14+Toc_IS!C13+HoldCo_IS!C10</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f>Cloud_IS!D14+Ind_IS!D14+Toc_IS!D13+HoldCo_IS!D10</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
+        <f>Cloud_IS!E14+Ind_IS!E14+Toc_IS!E13+HoldCo_IS!E10</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f>Cloud_IS!F14+Ind_IS!F14+Toc_IS!F13+HoldCo_IS!F10</f>
+        <v/>
+      </c>
+      <c r="G12" s="20">
+        <f>Cloud_IS!G14+Ind_IS!G14+Toc_IS!G13+HoldCo_IS!G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    管理费用</t>
+        </is>
+      </c>
+      <c r="C13" s="20">
+        <f>Cloud_IS!C15+Ind_IS!C15+Toc_IS!C14+HoldCo_IS!C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
+        <f>Cloud_IS!D15+Ind_IS!D15+Toc_IS!D14+HoldCo_IS!D11</f>
+        <v/>
+      </c>
+      <c r="E13" s="20">
+        <f>Cloud_IS!E15+Ind_IS!E15+Toc_IS!E14+HoldCo_IS!E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="20">
+        <f>Cloud_IS!F15+Ind_IS!F15+Toc_IS!F14+HoldCo_IS!F11</f>
+        <v/>
+      </c>
+      <c r="G13" s="20">
+        <f>Cloud_IS!G15+Ind_IS!G15+Toc_IS!G14+HoldCo_IS!G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    合并 EBIT</t>
+        </is>
+      </c>
+      <c r="C14" s="17">
+        <f>Consol_IS!C10-Consol_IS!C11-Consol_IS!C12-Consol_IS!C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>Consol_IS!D10-Consol_IS!D11-Consol_IS!D12-Consol_IS!D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>Consol_IS!E10-Consol_IS!E11-Consol_IS!E12-Consol_IS!E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>Consol_IS!F10-Consol_IS!F11-Consol_IS!F12-Consol_IS!F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>Consol_IS!G10-Consol_IS!G11-Consol_IS!G12-Consol_IS!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    所得税（Σ）</t>
+        </is>
+      </c>
+      <c r="C15" s="20">
+        <f>Cloud_IS!C17+Ind_IS!C17+Toc_IS!C16+HoldCo_IS!C13</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
+        <f>Cloud_IS!D17+Ind_IS!D17+Toc_IS!D16+HoldCo_IS!D13</f>
+        <v/>
+      </c>
+      <c r="E15" s="20">
+        <f>Cloud_IS!E17+Ind_IS!E17+Toc_IS!E16+HoldCo_IS!E13</f>
+        <v/>
+      </c>
+      <c r="F15" s="20">
+        <f>Cloud_IS!F17+Ind_IS!F17+Toc_IS!F16+HoldCo_IS!F13</f>
+        <v/>
+      </c>
+      <c r="G15" s="20">
+        <f>Cloud_IS!G17+Ind_IS!G17+Toc_IS!G16+HoldCo_IS!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    合并净利润</t>
+        </is>
+      </c>
+      <c r="C16" s="17">
+        <f>Consol_IS!C14-Consol_IS!C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>Consol_IS!D14-Consol_IS!D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>Consol_IS!E14-Consol_IS!E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>Consol_IS!F14-Consol_IS!F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>Consol_IS!G14-Consol_IS!G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    少数股东损益（E3）</t>
+        </is>
+      </c>
+      <c r="C17" s="20">
+        <f>Eliminations!C22</f>
+        <v/>
+      </c>
+      <c r="D17" s="20">
+        <f>Eliminations!D22</f>
+        <v/>
+      </c>
+      <c r="E17" s="20">
+        <f>Eliminations!E22</f>
+        <v/>
+      </c>
+      <c r="F17" s="20">
+        <f>Eliminations!F22</f>
+        <v/>
+      </c>
+      <c r="G17" s="20">
+        <f>Eliminations!G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    归属于母公司净利润</t>
+        </is>
+      </c>
+      <c r="C18" s="22">
+        <f>Consol_IS!C16-Consol_IS!C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>Consol_IS!D16-Consol_IS!D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>Consol_IS!E16-Consol_IS!E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="22">
+        <f>Consol_IS!F16-Consol_IS!F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="22">
+        <f>Consol_IS!G16-Consol_IS!G17</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B050"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>智擎集团 · 合并资产负债表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Σ四主体 − E0 − E2 + 少数股东权益 | 万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>科目（万元）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    货币资金</t>
+        </is>
+      </c>
+      <c r="C4" s="20">
+        <f>HoldCo_BS!C18+Cloud_BS_CF!C15+Ind_BS_CF!C12+Toc_BS_CF!C12</f>
+        <v/>
+      </c>
+      <c r="D4" s="20">
+        <f>HoldCo_BS!D18+Cloud_BS_CF!D15+Ind_BS_CF!D12+Toc_BS_CF!D12</f>
+        <v/>
+      </c>
+      <c r="E4" s="20">
+        <f>HoldCo_BS!E18+Cloud_BS_CF!E15+Ind_BS_CF!E12+Toc_BS_CF!E12</f>
+        <v/>
+      </c>
+      <c r="F4" s="20">
+        <f>HoldCo_BS!F18+Cloud_BS_CF!F15+Ind_BS_CF!F12+Toc_BS_CF!F12</f>
+        <v/>
+      </c>
+      <c r="G4" s="20">
+        <f>HoldCo_BS!G18+Cloud_BS_CF!G15+Ind_BS_CF!G12+Toc_BS_CF!G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    应收账款</t>
+        </is>
+      </c>
+      <c r="C5" s="20">
+        <f>HoldCo_BS!C4+Cloud_BS_CF!C5+Ind_BS_CF!C5+Toc_BS_CF!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>HoldCo_BS!D4+Cloud_BS_CF!D5+Ind_BS_CF!D5+Toc_BS_CF!D5</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>HoldCo_BS!E4+Cloud_BS_CF!E5+Ind_BS_CF!E5+Toc_BS_CF!E5</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>HoldCo_BS!F4+Cloud_BS_CF!F5+Ind_BS_CF!F5+Toc_BS_CF!F5</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>HoldCo_BS!G4+Cloud_BS_CF!G5+Ind_BS_CF!G5+Toc_BS_CF!G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    固定资产 · GPU 净值</t>
+        </is>
+      </c>
+      <c r="C6" s="20">
+        <f>HoldCo_BS!C6+Cloud_BS_CF!C7</f>
+        <v/>
+      </c>
+      <c r="D6" s="20">
+        <f>HoldCo_BS!D6+Cloud_BS_CF!D7</f>
+        <v/>
+      </c>
+      <c r="E6" s="20">
+        <f>HoldCo_BS!E6+Cloud_BS_CF!E7</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>HoldCo_BS!F6+Cloud_BS_CF!F7</f>
+        <v/>
+      </c>
+      <c r="G6" s="20">
+        <f>HoldCo_BS!G6+Cloud_BS_CF!G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    内部应收（抵消后 0）</t>
+        </is>
+      </c>
+      <c r="C7" s="20">
+        <f>HoldCo_BS!C5+Cloud_BS_CF!C6-Eliminations!C19</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>HoldCo_BS!D5+Cloud_BS_CF!D6-Eliminations!D19</f>
+        <v/>
+      </c>
+      <c r="E7" s="20">
+        <f>HoldCo_BS!E5+Cloud_BS_CF!E6-Eliminations!E19</f>
+        <v/>
+      </c>
+      <c r="F7" s="20">
+        <f>HoldCo_BS!F5+Cloud_BS_CF!F6-Eliminations!F19</f>
+        <v/>
+      </c>
+      <c r="G7" s="20">
+        <f>HoldCo_BS!G5+Cloud_BS_CF!G6-Eliminations!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    长期股权投资（抵消后 0）</t>
+        </is>
+      </c>
+      <c r="C8" s="20">
+        <f>HoldCo_BS!C7-Eliminations!C7-Eliminations!C10-Eliminations!C13</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>HoldCo_BS!D7-Eliminations!D7-Eliminations!D10-Eliminations!D13</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>HoldCo_BS!E7-Eliminations!E7-Eliminations!E10-Eliminations!E13</f>
+        <v/>
+      </c>
+      <c r="F8" s="20">
+        <f>HoldCo_BS!F7-Eliminations!F7-Eliminations!F10-Eliminations!F13</f>
+        <v/>
+      </c>
+      <c r="G8" s="20">
+        <f>HoldCo_BS!G7-Eliminations!G7-Eliminations!G10-Eliminations!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>资产总计</t>
+        </is>
+      </c>
+      <c r="C9" s="17">
+        <f>Consol_BS!C4+Consol_BS!C5+Consol_BS!C6</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
+        <f>Consol_BS!D4+Consol_BS!D5+Consol_BS!D6</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>Consol_BS!E4+Consol_BS!E5+Consol_BS!E6</f>
+        <v/>
+      </c>
+      <c r="F9" s="17">
+        <f>Consol_BS!F4+Consol_BS!F5+Consol_BS!F6</f>
+        <v/>
+      </c>
+      <c r="G9" s="17">
+        <f>Consol_BS!G4+Consol_BS!G5+Consol_BS!G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    应付账款</t>
+        </is>
+      </c>
+      <c r="C11" s="20">
+        <f>HoldCo_BS!C10+Cloud_BS_CF!C9+Ind_BS_CF!C7+Toc_BS_CF!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
+        <f>HoldCo_BS!D10+Cloud_BS_CF!D9+Ind_BS_CF!D7+Toc_BS_CF!D7</f>
+        <v/>
+      </c>
+      <c r="E11" s="20">
+        <f>HoldCo_BS!E10+Cloud_BS_CF!E9+Ind_BS_CF!E7+Toc_BS_CF!E7</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>HoldCo_BS!F10+Cloud_BS_CF!F9+Ind_BS_CF!F7+Toc_BS_CF!F7</f>
+        <v/>
+      </c>
+      <c r="G11" s="20">
+        <f>HoldCo_BS!G10+Cloud_BS_CF!G9+Ind_BS_CF!G7+Toc_BS_CF!G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    递延收益</t>
+        </is>
+      </c>
+      <c r="C12" s="20">
+        <f>HoldCo_BS!C12+Cloud_BS_CF!C11+Ind_BS_CF!C8+Toc_BS_CF!C8</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f>HoldCo_BS!D12+Cloud_BS_CF!D11+Ind_BS_CF!D8+Toc_BS_CF!D8</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
+        <f>HoldCo_BS!E12+Cloud_BS_CF!E11+Ind_BS_CF!E8+Toc_BS_CF!E8</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f>HoldCo_BS!F12+Cloud_BS_CF!F11+Ind_BS_CF!F8+Toc_BS_CF!F8</f>
+        <v/>
+      </c>
+      <c r="G12" s="20">
+        <f>HoldCo_BS!G12+Cloud_BS_CF!G11+Ind_BS_CF!G8+Toc_BS_CF!G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    内部应付（抵消后=在途差额）</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>按双边孰低抵消，剩余挂 other_pay</t>
+        </is>
+      </c>
+      <c r="C13" s="20">
+        <f>HoldCo_BS!C11+Cloud_BS_CF!C10+Ind_BS_CF!C6+Toc_BS_CF!C6-Eliminations!C19</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
+        <f>HoldCo_BS!D11+Cloud_BS_CF!D10+Ind_BS_CF!D6+Toc_BS_CF!D6-Eliminations!D19</f>
+        <v/>
+      </c>
+      <c r="E13" s="20">
+        <f>HoldCo_BS!E11+Cloud_BS_CF!E10+Ind_BS_CF!E6+Toc_BS_CF!E6-Eliminations!E19</f>
+        <v/>
+      </c>
+      <c r="F13" s="20">
+        <f>HoldCo_BS!F11+Cloud_BS_CF!F10+Ind_BS_CF!F6+Toc_BS_CF!F6-Eliminations!F19</f>
+        <v/>
+      </c>
+      <c r="G13" s="20">
+        <f>HoldCo_BS!G11+Cloud_BS_CF!G10+Ind_BS_CF!G6+Toc_BS_CF!G6-Eliminations!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    其他应付款 · 内部在途</t>
+        </is>
+      </c>
+      <c r="C14" s="20">
+        <f>Eliminations!C20</f>
+        <v/>
+      </c>
+      <c r="D14" s="20">
+        <f>Eliminations!D20</f>
+        <v/>
+      </c>
+      <c r="E14" s="20">
+        <f>Eliminations!E20</f>
+        <v/>
+      </c>
+      <c r="F14" s="20">
+        <f>Eliminations!F20</f>
+        <v/>
+      </c>
+      <c r="G14" s="20">
+        <f>Eliminations!G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>负债合计</t>
+        </is>
+      </c>
+      <c r="C15" s="17">
+        <f>Consol_BS!C11+Consol_BS!C12+Consol_BS!C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>Consol_BS!D11+Consol_BS!D12+Consol_BS!D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>Consol_BS!E11+Consol_BS!E12+Consol_BS!E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>Consol_BS!F11+Consol_BS!F12+Consol_BS!F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>Consol_BS!G11+Consol_BS!G12+Consol_BS!G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    实收资本（研究院口径）</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>子公司全抵</t>
+        </is>
+      </c>
+      <c r="C16" s="20">
+        <f>HoldCo_BS!C14</f>
+        <v/>
+      </c>
+      <c r="D16" s="20">
+        <f>HoldCo_BS!D14</f>
+        <v/>
+      </c>
+      <c r="E16" s="20">
+        <f>HoldCo_BS!E14</f>
+        <v/>
+      </c>
+      <c r="F16" s="20">
+        <f>HoldCo_BS!F14</f>
+        <v/>
+      </c>
+      <c r="G16" s="20">
+        <f>HoldCo_BS!G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    合并调整 · 资本公积（E0 差额）</t>
+        </is>
+      </c>
+      <c r="C17" s="20">
+        <f>Eliminations!C14</f>
+        <v/>
+      </c>
+      <c r="D17" s="20">
+        <f>Eliminations!D14</f>
+        <v/>
+      </c>
+      <c r="E17" s="20">
+        <f>Eliminations!E14</f>
+        <v/>
+      </c>
+      <c r="F17" s="20">
+        <f>Eliminations!F14</f>
+        <v/>
+      </c>
+      <c r="G17" s="20">
+        <f>Eliminations!G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    未分配利润（研究院口径）</t>
+        </is>
+      </c>
+      <c r="C18" s="20">
+        <f>HoldCo_BS!C15</f>
+        <v/>
+      </c>
+      <c r="D18" s="20">
+        <f>HoldCo_BS!D15</f>
+        <v/>
+      </c>
+      <c r="E18" s="20">
+        <f>HoldCo_BS!E15</f>
+        <v/>
+      </c>
+      <c r="F18" s="20">
+        <f>HoldCo_BS!F15</f>
+        <v/>
+      </c>
+      <c r="G18" s="20">
+        <f>HoldCo_BS!G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    少数股东权益（E3）</t>
+        </is>
+      </c>
+      <c r="C19" s="20">
+        <f>Eliminations!C23</f>
+        <v/>
+      </c>
+      <c r="D19" s="20">
+        <f>Eliminations!D23</f>
+        <v/>
+      </c>
+      <c r="E19" s="20">
+        <f>Eliminations!E23</f>
+        <v/>
+      </c>
+      <c r="F19" s="20">
+        <f>Eliminations!F23</f>
+        <v/>
+      </c>
+      <c r="G19" s="20">
+        <f>Eliminations!G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>合并所有者权益合计</t>
+        </is>
+      </c>
+      <c r="C20" s="17">
+        <f>Consol_BS!C16+Consol_BS!C17+Consol_BS!C18+Consol_BS!C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>Consol_BS!D16+Consol_BS!D17+Consol_BS!D18+Consol_BS!D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
+        <f>Consol_BS!E16+Consol_BS!E17+Consol_BS!E18+Consol_BS!E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="17">
+        <f>Consol_BS!F16+Consol_BS!F17+Consol_BS!F18+Consol_BS!F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="17">
+        <f>Consol_BS!G16+Consol_BS!G17+Consol_BS!G18+Consol_BS!G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>负债+权益合计</t>
+        </is>
+      </c>
+      <c r="C21" s="17">
+        <f>Consol_BS!C15+Consol_BS!C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>Consol_BS!D15+Consol_BS!D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>Consol_BS!E15+Consol_BS!E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="17">
+        <f>Consol_BS!F15+Consol_BS!F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="17">
+        <f>Consol_BS!G15+Consol_BS!G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>★ 合并 BS 平衡差（应全 0）</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  资产 − 负债 − 权益</t>
+        </is>
+      </c>
+      <c r="C23" s="23">
+        <f>Consol_BS!C9-Consol_BS!C21</f>
+        <v/>
+      </c>
+      <c r="D23" s="23">
+        <f>Consol_BS!D9-Consol_BS!D21</f>
+        <v/>
+      </c>
+      <c r="E23" s="23">
+        <f>Consol_BS!E9-Consol_BS!E21</f>
+        <v/>
+      </c>
+      <c r="F23" s="23">
+        <f>Consol_BS!F9-Consol_BS!F21</f>
+        <v/>
+      </c>
+      <c r="G23" s="23">
+        <f>Consol_BS!G9-Consol_BS!G21</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B050"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>智擎集团 · 合并现金流量表（间接法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>合并 NI+D&amp;A+ΔWC；内部结算不出合并范围自动消失 | 万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>科目（万元）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    合并净利润</t>
+        </is>
+      </c>
+      <c r="C4" s="20">
+        <f>Consol_IS!C16</f>
+        <v/>
+      </c>
+      <c r="D4" s="20">
+        <f>Consol_IS!D16</f>
+        <v/>
+      </c>
+      <c r="E4" s="20">
+        <f>Consol_IS!E16</f>
+        <v/>
+      </c>
+      <c r="F4" s="20">
+        <f>Consol_IS!F16</f>
+        <v/>
+      </c>
+      <c r="G4" s="20">
+        <f>Consol_IS!G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    加：折旧（训练+推理）</t>
+        </is>
+      </c>
+      <c r="C5" s="20">
+        <f>Capex_Dep!C22+Capex_Dep!C24</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>Capex_Dep!D22+Capex_Dep!D24</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>Capex_Dep!E22+Capex_Dep!E24</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>Capex_Dep!F22+Capex_Dep!F24</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>Capex_Dep!G22+Capex_Dep!G24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    减：应收增加</t>
+        </is>
+      </c>
+      <c r="C6" s="20">
+        <f>-(Consol_BS!C5-(0))</f>
+        <v/>
+      </c>
+      <c r="D6" s="20">
+        <f>-(Consol_BS!D5-(Consol_BS!C5))</f>
+        <v/>
+      </c>
+      <c r="E6" s="20">
+        <f>-(Consol_BS!E5-(Consol_BS!D5))</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>-(Consol_BS!F5-(Consol_BS!E5))</f>
+        <v/>
+      </c>
+      <c r="G6" s="20">
+        <f>-(Consol_BS!G5-(Consol_BS!F5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    加：递延增加</t>
+        </is>
+      </c>
+      <c r="C7" s="20">
+        <f>Consol_BS!C12-(0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>Consol_BS!D12-(Consol_BS!C12)</f>
+        <v/>
+      </c>
+      <c r="E7" s="20">
+        <f>Consol_BS!E12-(Consol_BS!D12)</f>
+        <v/>
+      </c>
+      <c r="F7" s="20">
+        <f>Consol_BS!F12-(Consol_BS!E12)</f>
+        <v/>
+      </c>
+      <c r="G7" s="20">
+        <f>Consol_BS!G12-(Consol_BS!F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    加：应付增加</t>
+        </is>
+      </c>
+      <c r="C8" s="20">
+        <f>Consol_BS!C11-(0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>Consol_BS!D11-(Consol_BS!C11)</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>Consol_BS!E11-(Consol_BS!D11)</f>
+        <v/>
+      </c>
+      <c r="F8" s="20">
+        <f>Consol_BS!F11-(Consol_BS!E11)</f>
+        <v/>
+      </c>
+      <c r="G8" s="20">
+        <f>Consol_BS!G11-(Consol_BS!F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    加：在途挂账变动</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>非现金</t>
+        </is>
+      </c>
+      <c r="C9" s="20">
+        <f>Consol_BS!C14-(0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="20">
+        <f>Consol_BS!D14-(Consol_BS!C14)</f>
+        <v/>
+      </c>
+      <c r="E9" s="20">
+        <f>Consol_BS!E14-(Consol_BS!D14)</f>
+        <v/>
+      </c>
+      <c r="F9" s="20">
+        <f>Consol_BS!F14-(Consol_BS!E14)</f>
+        <v/>
+      </c>
+      <c r="G9" s="20">
+        <f>Consol_BS!G14-(Consol_BS!F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    经营活动现金流</t>
+        </is>
+      </c>
+      <c r="C10" s="17">
+        <f>Consol_CF!C4+Consol_CF!C5+Consol_CF!C6+Consol_CF!C7+Consol_CF!C8+Consol_CF!C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>Consol_CF!D4+Consol_CF!D5+Consol_CF!D6+Consol_CF!D7+Consol_CF!D8+Consol_CF!D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>Consol_CF!E4+Consol_CF!E5+Consol_CF!E6+Consol_CF!E7+Consol_CF!E8+Consol_CF!E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>Consol_CF!F4+Consol_CF!F5+Consol_CF!F6+Consol_CF!F7+Consol_CF!F8+Consol_CF!F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>Consol_CF!G4+Consol_CF!G5+Consol_CF!G6+Consol_CF!G7+Consol_CF!G8+Consol_CF!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    投资活动现金流</t>
+        </is>
+      </c>
+      <c r="C11" s="20">
+        <f>-Capex_Dep!C5-Capex_Dep!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
+        <f>-Capex_Dep!D5-Capex_Dep!D6</f>
+        <v/>
+      </c>
+      <c r="E11" s="20">
+        <f>-Capex_Dep!E5-Capex_Dep!E6</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>-Capex_Dep!F5-Capex_Dep!F6</f>
+        <v/>
+      </c>
+      <c r="G11" s="20">
+        <f>-Capex_Dep!G5-Capex_Dep!G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    筹资活动（研究院注资+互联战投）</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>子公司注资=内部划转，抵消</t>
+        </is>
+      </c>
+      <c r="C12" s="20">
+        <f>Assumptions!C56+Assumptions!C59*0.2</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f>Assumptions!D56+Assumptions!D59*0.2</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
+        <f>Assumptions!E56+Assumptions!E59*0.2</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f>Assumptions!F56+Assumptions!F59*0.2</f>
+        <v/>
+      </c>
+      <c r="G12" s="20">
+        <f>Assumptions!G56+Assumptions!G59*0.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    现金净变动</t>
+        </is>
+      </c>
+      <c r="C13" s="17">
+        <f>Consol_CF!C10+Consol_CF!C11+Consol_CF!C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>Consol_CF!D10+Consol_CF!D11+Consol_CF!D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>Consol_CF!E10+Consol_CF!E11+Consol_CF!E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>Consol_CF!F10+Consol_CF!F11+Consol_CF!F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>Consol_CF!G10+Consol_CF!G11+Consol_CF!G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    期末现金（CF 推导）</t>
+        </is>
+      </c>
+      <c r="C14" s="17">
+        <f>68000.00000100001+Consol_CF!C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>C14+Consol_CF!D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>D14+Consol_CF!E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>E14+Consol_CF!F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>F14+Consol_CF!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    期末现金（Σ单体 BS）</t>
+        </is>
+      </c>
+      <c r="C15" s="20">
+        <f>HoldCo_BS!C18+Cloud_BS_CF!C15+Ind_BS_CF!C12+Toc_BS_CF!C12</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
+        <f>HoldCo_BS!D18+Cloud_BS_CF!D15+Ind_BS_CF!D12+Toc_BS_CF!D12</f>
+        <v/>
+      </c>
+      <c r="E15" s="20">
+        <f>HoldCo_BS!E18+Cloud_BS_CF!E15+Ind_BS_CF!E12+Toc_BS_CF!E12</f>
+        <v/>
+      </c>
+      <c r="F15" s="20">
+        <f>HoldCo_BS!F18+Cloud_BS_CF!F15+Ind_BS_CF!F12+Toc_BS_CF!F12</f>
+        <v/>
+      </c>
+      <c r="G15" s="20">
+        <f>HoldCo_BS!G18+Cloud_BS_CF!G15+Ind_BS_CF!G12+Toc_BS_CF!G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>★ 合并 CF=BS 差异（应全 0）</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CF推导 − Σ单体现金</t>
+        </is>
+      </c>
+      <c r="C17" s="23">
+        <f>Consol_CF!C14-Consol_CF!C15</f>
+        <v/>
+      </c>
+      <c r="D17" s="23">
+        <f>Consol_CF!D14-Consol_CF!D15</f>
+        <v/>
+      </c>
+      <c r="E17" s="23">
+        <f>Consol_CF!E14-Consol_CF!E15</f>
+        <v/>
+      </c>
+      <c r="F17" s="23">
+        <f>Consol_CF!F14-Consol_CF!F15</f>
+        <v/>
+      </c>
+      <c r="G17" s="23">
+        <f>Consol_CF!G14-Consol_CF!G15</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
